--- a/output/pdf_financials_xlsx/FFP.xlsx
+++ b/output/pdf_financials_xlsx/FFP.xlsx
@@ -431,6 +431,14 @@
   </sheetPr>
   <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/FFP.xlsx
+++ b/output/pdf_financials_xlsx/FFP.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.144363</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.153248</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.140613</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.116067</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.14522</v>
       </c>
     </row>
     <row r="10">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -779,19 +779,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.011312</v>
+        <v>-0.011312</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.001509</v>
+        <v>0.001509</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.0606</v>
+        <v>0.0606</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.028098</v>
+        <v>0.028098</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.057682</v>
+        <v>0.057682</v>
       </c>
     </row>
     <row r="18">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.002218</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.002614</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.000752</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.000357</v>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.168334</v>
+        <v>0.170552</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.030475</v>
+        <v>0.033089</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.284601</v>
+        <v>-0.283849</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.143201</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>34.86540281807996</v>
+        <v>35.32479583108091</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>9.320854551849642</v>
+        <v>10.1203529537704</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2656,20 +2656,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.157022</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0.031984</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.224001</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.11546</v>
@@ -2684,20 +2678,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -2712,20 +2700,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -2740,20 +2722,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -2768,20 +2744,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -2796,20 +2766,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0</v>
@@ -2824,20 +2788,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -2852,20 +2810,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
@@ -2880,20 +2832,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0</v>
@@ -2908,20 +2854,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -2936,20 +2876,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -2964,20 +2898,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -2992,20 +2920,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3020,20 +2942,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -3048,20 +2964,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -3076,20 +2986,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -3104,20 +3008,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -3132,20 +3030,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -3160,20 +3052,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -3188,20 +3074,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -3216,15 +3096,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.015779</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-0.008245000000000001</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -3248,20 +3124,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -3276,20 +3146,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -3304,20 +3168,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -3332,20 +3190,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -3360,20 +3212,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -3388,20 +3234,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -3416,20 +3256,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -3476,20 +3310,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -3514,20 +3342,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="130">
@@ -3536,20 +3358,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.060315</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.081635</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.07856299999999999</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.109311</v>
@@ -3564,20 +3380,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -3592,20 +3402,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.02132</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.038977</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.030748</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0.098735</v>
@@ -3620,20 +3424,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.081635</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.042658</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.109311</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>0.208046</v>
@@ -3648,20 +3446,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3713,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4955,10 +4747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="5" t="n">
+        <v>0.000752</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0.000357</v>
@@ -4994,10 +4784,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G32" s="5" t="n">
+        <v>0.0024</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0.0024</v>
@@ -5033,10 +4821,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G33" s="5" t="n">
+        <v>0.350433</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0.210261</v>
@@ -5072,10 +4858,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G34" s="5" t="n">
+        <v>0.068984</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0.045243</v>
@@ -5111,10 +4895,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="5" t="n">
+        <v>0.001764</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0.003492</v>
@@ -5150,10 +4932,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G36" s="5" t="n">
+        <v>0.07074800000000001</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0.048735</v>
@@ -5353,10 +5133,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G41" s="5" t="n">
+        <v>0.07856299999999999</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0.109311</v>
@@ -5396,10 +5174,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" s="5" t="n">
+        <v>0.109311</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0.208046</v>
@@ -5450,20 +5226,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fee income (Note 12)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5475,36 +5255,32 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.327888</v>
+        <v>-0.224001</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.311884</v>
+        <v>-0.11546</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.330416</v>
+        <v>-0.316748</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other income (Note 12)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Adjustments for below-market CEBA loan (Note 7)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5515,30 +5291,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>0.003892</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.00379</v>
+        <v>-0.024217</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.003009</v>
+        <v>0.024217</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unrealized net loss on investments measured at</t>
+          <t>Unrealized net loss on revaluation of investments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unrealized net loss on investments measured at fair value through profit or loss (Note 5)</t>
+          <t>Deferred income tax (recovery) expense</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5553,29 +5331,29 @@
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.350433</v>
+        <v>-0.0606</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-0.210261</v>
+        <v>-0.028098</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-0.43152</v>
+        <v>-0.057682</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Unrealized net loss on investments measured at</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unrealized net loss on investments measured at total</t>
+          <t>Repayment of CEBA loan (Note 7)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5589,30 +5367,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.018653</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>0.105413</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.098095</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salaries and benefits (Note 12)</t>
+          <t>Decrease in amounts owing to related party (Note 12)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5627,32 +5409,36 @@
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.128613</v>
+        <v>-0.04</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.104067</v>
+        <v>-0.01</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.13322</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Office, administration and rent (Note 12)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -5664,66 +5450,68 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.08848399999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.093859</v>
+        <v>0.05</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.09283</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>0.034457</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0.030093</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.03</v>
+          <t>(Decrease) Increase in cash position during the year</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.03</v>
+        <v>0.098735</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>0.03</v>
+        <v>-0.043387</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Consulting (Note 12)</t>
+          <t>Increase in cash position during the year</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5738,470 +5526,486 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.012</v>
+        <v>0.030748</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>0.012</v>
+        <v>0.098735</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
-        <v>0.003618</v>
+        <v>0.157022</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.004014</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.002152</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0.001757</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0.001139</v>
+        <v>0.031984</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cumulative translation adjustment loss</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Cumulative translation adjustment loss realized from the wind-up of a foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.002299</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>0.00278</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>0.000529</v>
+      <c r="F53" s="5" t="n">
+        <v>0.018206</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cumulative translation adjustment loss</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.235805</v>
+        <v>0.002218</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.278274</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.263548</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0.244463</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>0.269718</v>
+        <v>0.002614</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Cumulative translation adjustment loss</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Interest expense (Note 7)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>InterestExpense</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>0.011312</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-0.001509</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n">
-        <v>-0.002108</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>-0.004217</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Cumulative translation adjustment loss</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Accrued dividends on redeemable preference shares (Note 8)</t>
+          <t>Cumulative translation adjustment loss total</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0024</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>-0.0024</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>-0.0024</v>
+      <c r="E56" s="5" t="n">
+        <v>0.170552</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.051295</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Decrease in non-cash operating working</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Other expenses total</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0024</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>-0.004508</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>-0.006617</v>
+          <t>Decrease in non-cash operating working capital (Note 14)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>-0.133347</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-0.082028</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Decrease in non-cash operating working</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.284601</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>-0.143558</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>-0.37443</v>
+          <t>Decrease in non-cash operating working total</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0.037205</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>-0.030733</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense (Note 10)</t>
+          <t>Fixed assets purchased</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="5" t="n">
+        <v>-0.007913999999999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0606</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>-0.028098</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>-0.057682</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.224001</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>-0.11546</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>-0.316748</v>
+          <t>Increase in long-term receivable</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>-0.012804</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-0.008245000000000001</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net proceeds on sale of investments</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>0.004939</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares (Note 16)</t>
+          <t>Investing activities total</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>6.171703</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>6.171703</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>6.171703</v>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-0.015779</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.008245000000000001</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fee income (Note 15)</t>
+          <t>Foreign exchange on cash</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.31291</v>
+        <v>-0.000106</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.324146</v>
+        <v>1e-06</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6222,29 +6026,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Other income (Note 15)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>(Decrease) increase in cash position during the year</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.002569</v>
+        <v>0.02132</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.002809</v>
+        <v>-0.038977</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6265,27 +6065,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sale of condominium unit (Note 6)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>0.165682</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.060315</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.081635</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6306,27 +6108,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rental income</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
-        <v>0.00165</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.081635</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.042658</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -6357,34 +6161,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Revenue total</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0.482811</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.326955</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Fee income (Note 12)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.327888</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.311884</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.330416</v>
       </c>
     </row>
     <row r="68">
@@ -6400,36 +6198,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cost of sales (Note 6)</t>
+          <t>Other income (Note 12)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0.07867200000000001</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>0.003892</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.00379</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.003009</v>
       </c>
     </row>
     <row r="69">
@@ -6440,35 +6234,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Unrealized net loss on investments measured at</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gross income</t>
+          <t>Unrealized net loss on investments measured at fair value through profit or loss (Note 5)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.404139</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0.326955</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-0.350433</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>-0.210261</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-0.43152</v>
       </c>
     </row>
     <row r="70">
@@ -6479,35 +6271,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized net loss on investments measured at</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salaries and benefits (Note 15)</t>
+          <t>Unrealized net loss on investments measured at total</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.144137</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>0.153009</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.018653</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.105413</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.098095</v>
       </c>
     </row>
     <row r="71">
@@ -6523,30 +6313,32 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Office, administration and rent (Note 15)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.08638700000000001</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0.08455699999999999</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Salaries and benefits (Note 12)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.128613</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.104067</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.13322</v>
       </c>
     </row>
     <row r="72">
@@ -6562,34 +6354,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>-0.03302</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.006362</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office, administration and rent (Note 12)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.08848399999999999</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.093859</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.09283</v>
       </c>
     </row>
     <row r="73">
@@ -6605,30 +6391,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
-        <v>0.000226</v>
+        <v>0.034457</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.000239</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030093</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="74">
@@ -6639,37 +6423,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss realized from the wind-up of a foreign subsidiary</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Consulting (Note 12)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.018206</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="75">
@@ -6680,37 +6464,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss total</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>0.003618</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.018206</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004014</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.002152</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.001139</v>
       </c>
     </row>
     <row r="76">
@@ -6721,39 +6497,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>0.168334</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.030475</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.002299</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0.000529</v>
       </c>
     </row>
     <row r="77">
@@ -6764,35 +6538,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense (Note 13)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
-        <v>0.011312</v>
+        <v>0.235805</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.001509</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.278274</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.263548</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.244463</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.269718</v>
       </c>
     </row>
     <row r="78">
@@ -6803,39 +6575,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment loss</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
+          <t>Interest expense (Note 7)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>0.157022</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>0.031984</v>
+          <t>InterestExpense</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>-0.002108</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-0.004217</v>
       </c>
     </row>
     <row r="79">
@@ -6846,35 +6618,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on available-for-sale investments</t>
+          <t>Accrued dividends on redeemable preference shares (Note 8)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>-0.142005</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.107361</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.0024</v>
       </c>
     </row>
     <row r="80">
@@ -6885,35 +6655,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation of foreign subsidiary</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>-0.012618</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.018206</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other expenses total</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0.004508</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0.006617</v>
       </c>
     </row>
     <row r="81">
@@ -6924,35 +6696,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>-0.154623</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0.125567</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.284601</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-0.143558</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>-0.37443</v>
       </c>
     </row>
     <row r="82">
@@ -6963,35 +6737,33 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Comprehensive income for the year</t>
+          <t>Income tax (recovery) expense (Note 10)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.002399</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.157551</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.0606</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>-0.028098</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.057682</v>
       </c>
     </row>
     <row r="83">
@@ -7002,12 +6774,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7015,26 +6787,24 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>0.157022</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.031984</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-0.224001</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>-0.11546</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.316748</v>
       </c>
     </row>
     <row r="84">
@@ -7045,35 +6815,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>-3.478905</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>-3.321883</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>-5e-08</v>
       </c>
     </row>
     <row r="85">
@@ -7084,35 +6856,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Changes in unrealized gains/(losses) on translation</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Deficit, end of year</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>-3.321883</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>-3.289899</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares (Note 16)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>6.171703</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>6.171703</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>6.171703</v>
       </c>
     </row>
     <row r="86">
@@ -7123,24 +6897,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Fee income (Note 15)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.31291</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.324146</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7166,32 +6936,979 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Other income (Note 15)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.002569</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.002809</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sale of condominium unit (Note 6)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.165682</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Rental income</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Revenue total</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.482811</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.326955</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Cost of sales (Note 6)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.07867200000000001</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Gross income</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>0.404139</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.326955</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salaries and benefits (Note 15)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0.144137</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.153009</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Office, administration and rent (Note 15)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>0.08638700000000001</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.08455699999999999</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.03302</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0.006362</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Travel and promotion</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.000239</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss realized from the wind-up of a foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>-0.018206</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss total</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-0.018206</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.168334</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.030475</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Income tax (recovery) expense (Note 13)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>0.011312</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-0.001509</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment loss</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.157022</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.031984</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on available-for-sale investments</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>-0.142005</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.107361</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation of foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>-0.012618</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.018206</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>-0.154623</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.125567</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>0.002399</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.157551</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.157022</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.031984</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>-3.478905</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-3.321883</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Changes in unrealized gains/(losses) on translation</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Deficit, end of year</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>-3.321883</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-3.289899</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Basic and diluted</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
         <v>6.006703</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F110" s="5" t="n">
         <v>6.006703</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/FFP.xlsx
+++ b/output/pdf_financials_xlsx/FFP.xlsx
@@ -1178,13 +1178,13 @@
         <v>0.042658</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.109311</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.208046</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.164659</v>
       </c>
     </row>
     <row r="35">
@@ -1222,13 +1222,13 @@
         <v>0.042658</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.109311</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.208046</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.164659</v>
       </c>
     </row>
     <row r="37">
@@ -1486,13 +1486,13 @@
         <v>0.003454</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.112757</v>
+        <v>0.003446</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.211501</v>
+        <v>0.003455</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.165089</v>
+        <v>0.00043</v>
       </c>
     </row>
     <row r="49">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">

--- a/output/pdf_financials_xlsx/FFP.xlsx
+++ b/output/pdf_financials_xlsx/FFP.xlsx
@@ -6745,7 +6745,11 @@
           <t>Income tax (recovery) expense (Note 10)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7489,7 +7493,11 @@
           <t>Income tax (recovery) expense (Note 13)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>0.011312</v>
       </c>
